--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count-reversed.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count-reversed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B8AAB90-EAE6-4AAC-8529-26C91E86CF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AABA655F-D599-46A9-B97E-2682BE36C95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{623F3243-920A-4980-91BE-010DEB56145A}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{EEA7D122-826B-4344-A731-B28AA53CCAAE}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576858912034" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{C805F047-2399-4258-A808-6486C2FD9964}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579422337963" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{65881AC7-9664-4AD5-904E-4597C3FB6600}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{258615A2-4963-4806-B6F8-9D0D66C50423}" name="AllErrorPivot" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9FFA0477-F33F-43FA-8602-5D6DB12A591E}" name="AllErrorPivot" cacheId="47" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -531,7 +531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26769370-B492-48C7-BDB9-A9314FA6949D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6ABF6F2-E892-4503-9768-DDB5CA37180F}">
   <dimension ref="A4:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746BF131-770C-4FAF-B370-29D1C5C05A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D90DED0-57AB-496B-90A2-B93FD8A03716}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
